--- a/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
+++ b/jpcore-r4/feature/swg2_diagnosticreport-radiology/StructureDefinition-jp-observation-dentaloral-missingtoothcondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3793" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3794" uniqueCount="555">
   <si>
     <t>Property</t>
   </si>
@@ -617,7 +617,10 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -642,7 +645,10 @@
     <t>このObservationに関する分類（JP_SimpleObservationCategory_VS）、必須項目</t>
   </si>
   <si>
-    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+    <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
     <t>Observation.category:first.id</t>
@@ -898,10 +904,10 @@
     <t>second</t>
   </si>
   <si>
-    <t>このObservationに関するLOINC上の分類、必須項目</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationDentalCategory_VS</t>
+    <t>第2カテゴリはLOINCのコードLP89803-8固定とする、ValueSetのバインディングを指定していないことに注意すること</t>
+  </si>
+  <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
   </si>
   <si>
     <t>Observation.category:second.id</t>
@@ -1352,10 +1358,7 @@
 2.厚生労働省標準標準歯式マスタ、レセプト電算処理用コード</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -3852,22 +3855,24 @@
       <c r="X15" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y15" s="2"/>
+      <c r="Y15" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>186</v>
@@ -3894,10 +3899,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3905,13 +3910,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>83</v>
@@ -3921,7 +3926,7 @@
         <v>94</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
@@ -3936,13 +3941,13 @@
         <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>191</v>
@@ -3974,7 +3979,7 @@
       </c>
       <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -4016,10 +4021,10 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -4027,10 +4032,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4053,13 +4058,13 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4110,7 +4115,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4134,7 +4139,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4145,10 +4150,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4177,7 +4182,7 @@
         <v>141</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>143</v>
@@ -4218,19 +4223,19 @@
         <v>83</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4254,7 +4259,7 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>83</v>
@@ -4265,10 +4270,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4291,19 +4296,19 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4352,7 +4357,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4373,10 +4378,10 @@
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4387,10 +4392,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4413,13 +4418,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4470,7 +4475,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4494,7 +4499,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4505,10 +4510,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4537,7 +4542,7 @@
         <v>141</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>143</v>
@@ -4578,19 +4583,19 @@
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4614,7 +4619,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4625,10 +4630,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4654,23 +4659,23 @@
         <v>108</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>83</v>
@@ -4712,7 +4717,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4733,10 +4738,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4747,10 +4752,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4773,16 +4778,16 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4832,7 +4837,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4853,10 +4858,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4867,10 +4872,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4896,21 +4901,21 @@
         <v>114</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4952,7 +4957,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4973,10 +4978,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4987,10 +4992,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5013,17 +5018,17 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5072,7 +5077,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5093,10 +5098,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5107,10 +5112,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5133,19 +5138,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5194,7 +5199,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5215,10 +5220,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5229,10 +5234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5255,19 +5260,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5316,7 +5321,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5337,10 +5342,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5351,13 +5356,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5382,13 +5387,13 @@
         <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>200</v>
+        <v>287</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>191</v>
@@ -5416,11 +5421,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>285</v>
+        <v>193</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5462,10 +5469,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5473,10 +5480,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5499,13 +5506,13 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5556,7 +5563,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5580,7 +5587,7 @@
         <v>83</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5591,10 +5598,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5623,7 +5630,7 @@
         <v>141</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N30" t="s" s="2">
         <v>143</v>
@@ -5664,19 +5671,19 @@
         <v>83</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5700,7 +5707,7 @@
         <v>83</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -5711,10 +5718,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5737,19 +5744,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5798,7 +5805,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5819,10 +5826,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5833,10 +5840,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5859,13 +5866,13 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5916,7 +5923,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5940,7 +5947,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5951,10 +5958,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5983,7 +5990,7 @@
         <v>141</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N33" t="s" s="2">
         <v>143</v>
@@ -6024,19 +6031,19 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6060,7 +6067,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6071,10 +6078,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6100,23 +6107,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6158,7 +6165,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6179,10 +6186,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6193,10 +6200,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6219,16 +6226,16 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6278,7 +6285,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6299,10 +6306,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6313,10 +6320,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6342,21 +6349,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6398,7 +6405,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6419,10 +6426,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6433,10 +6440,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6459,17 +6466,17 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6518,7 +6525,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6539,10 +6546,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6553,10 +6560,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6579,19 +6586,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6640,7 +6647,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6661,10 +6668,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6675,10 +6682,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6701,19 +6708,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6762,7 +6769,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6783,10 +6790,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6797,13 +6804,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>186</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>83</v>
@@ -6828,13 +6835,13 @@
         <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>200</v>
+        <v>287</v>
       </c>
       <c r="O40" t="s" s="2">
         <v>191</v>
@@ -6866,7 +6873,7 @@
       </c>
       <c r="Y40" s="2"/>
       <c r="Z40" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6908,10 +6915,10 @@
         <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -6919,10 +6926,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6945,13 +6952,13 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7002,7 +7009,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7026,7 +7033,7 @@
         <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7037,10 +7044,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7069,7 +7076,7 @@
         <v>141</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>143</v>
@@ -7110,19 +7117,19 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7146,7 +7153,7 @@
         <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7157,10 +7164,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7183,19 +7190,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7244,7 +7251,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7265,10 +7272,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7279,10 +7286,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7305,13 +7312,13 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7362,7 +7369,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7386,7 +7393,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7397,10 +7404,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7429,7 +7436,7 @@
         <v>141</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>143</v>
@@ -7470,19 +7477,19 @@
         <v>83</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7506,7 +7513,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7517,10 +7524,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7546,23 +7553,23 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7604,7 +7611,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7625,10 +7632,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7639,10 +7646,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7665,16 +7672,16 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7724,7 +7731,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7745,10 +7752,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7759,10 +7766,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7788,21 +7795,21 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -7844,7 +7851,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7865,10 +7872,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7879,10 +7886,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7905,17 +7912,17 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7964,7 +7971,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7985,10 +7992,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7999,10 +8006,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8025,19 +8032,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8086,7 +8093,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8107,10 +8114,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8121,10 +8128,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8147,19 +8154,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8208,7 +8215,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8229,10 +8236,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8243,14 +8250,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8272,16 +8279,16 @@
         <v>188</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8306,13 +8313,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8330,7 +8337,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>94</v>
@@ -8345,30 +8352,30 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8391,13 +8398,13 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8448,7 +8455,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8472,7 +8479,7 @@
         <v>83</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8483,10 +8490,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8515,7 +8522,7 @@
         <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N54" t="s" s="2">
         <v>143</v>
@@ -8556,19 +8563,19 @@
         <v>83</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8592,7 +8599,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8603,10 +8610,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8629,19 +8636,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8690,7 +8697,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8711,10 +8718,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8725,10 +8732,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8751,13 +8758,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8808,7 +8815,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8832,7 +8839,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8843,10 +8850,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8875,7 +8882,7 @@
         <v>141</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>143</v>
@@ -8916,19 +8923,19 @@
         <v>83</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8952,7 +8959,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8963,10 +8970,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8992,23 +8999,23 @@
         <v>108</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>83</v>
@@ -9050,7 +9057,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9071,10 +9078,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9085,10 +9092,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9111,16 +9118,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9170,7 +9177,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9191,10 +9198,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9205,10 +9212,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9234,21 +9241,21 @@
         <v>114</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>83</v>
@@ -9290,7 +9297,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9311,10 +9318,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9325,10 +9332,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9351,17 +9358,17 @@
         <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9371,7 +9378,7 @@
         <v>83</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>83</v>
@@ -9410,7 +9417,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9431,10 +9438,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9445,10 +9452,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9471,19 +9478,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9532,7 +9539,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9553,10 +9560,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9567,10 +9574,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9593,19 +9600,19 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9654,7 +9661,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9675,10 +9682,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9689,10 +9696,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9715,19 +9722,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9776,7 +9783,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9791,19 +9798,19 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>83</v>
@@ -9811,10 +9818,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9837,7 +9844,7 @@
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>162</v>
@@ -9846,7 +9853,7 @@
         <v>162</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9896,7 +9903,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9917,13 +9924,13 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9931,14 +9938,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9957,19 +9964,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10018,7 +10025,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10033,19 +10040,19 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>83</v>
@@ -10053,14 +10060,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10079,19 +10086,19 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10140,7 +10147,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10155,19 +10162,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>83</v>
@@ -10175,10 +10182,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10201,16 +10208,16 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10260,7 +10267,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10281,13 +10288,13 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>83</v>
@@ -10295,10 +10302,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10321,19 +10328,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10382,7 +10389,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10397,19 +10404,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>83</v>
@@ -10417,10 +10424,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10446,16 +10453,16 @@
         <v>188</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10504,7 +10511,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10513,7 +10520,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -10522,27 +10529,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10568,16 +10575,16 @@
         <v>188</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10602,13 +10609,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10626,7 +10633,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10635,7 +10642,7 @@
         <v>94</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>106</v>
@@ -10650,7 +10657,7 @@
         <v>137</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10661,14 +10668,14 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -10696,10 +10703,10 @@
         <v>162</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10724,13 +10731,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10748,7 +10755,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10766,27 +10773,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10809,7 +10816,7 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L73" t="s" s="2">
         <v>162</v>
@@ -10818,10 +10825,10 @@
         <v>162</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10870,7 +10877,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10891,10 +10898,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -10905,10 +10912,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10934,13 +10941,13 @@
         <v>188</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10966,13 +10973,11 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10990,7 +10995,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11008,27 +11013,27 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11054,16 +11059,16 @@
         <v>188</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11088,13 +11093,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11112,7 +11117,7 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11133,10 +11138,10 @@
         <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
@@ -11147,10 +11152,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11173,7 +11178,7 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>162</v>
@@ -11182,7 +11187,7 @@
         <v>162</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11232,7 +11237,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11250,27 +11255,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11293,16 +11298,16 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11352,7 +11357,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11370,27 +11375,27 @@
         <v>83</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11413,7 +11418,7 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>162</v>
@@ -11422,10 +11427,10 @@
         <v>162</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>83</v>
@@ -11474,7 +11479,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11486,7 +11491,7 @@
         <v>83</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>83</v>
@@ -11495,10 +11500,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11509,10 +11514,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11535,13 +11540,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11592,7 +11597,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11616,7 +11621,7 @@
         <v>83</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11627,10 +11632,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11659,7 +11664,7 @@
         <v>141</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>143</v>
@@ -11712,7 +11717,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -11736,7 +11741,7 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -11747,14 +11752,14 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11776,10 +11781,10 @@
         <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>143</v>
@@ -11834,7 +11839,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11869,10 +11874,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11895,13 +11900,13 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11952,7 +11957,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11961,7 +11966,7 @@
         <v>94</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>106</v>
@@ -11973,10 +11978,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -11987,10 +11992,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12013,13 +12018,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12070,7 +12075,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12079,7 +12084,7 @@
         <v>94</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>106</v>
@@ -12091,10 +12096,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12105,10 +12110,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12134,16 +12139,16 @@
         <v>188</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>83</v>
@@ -12171,10 +12176,10 @@
         <v>118</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>83</v>
@@ -12192,7 +12197,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12210,13 +12215,13 @@
         <v>83</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12227,10 +12232,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12256,16 +12261,16 @@
         <v>188</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12290,13 +12295,13 @@
         <v>83</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>83</v>
@@ -12314,7 +12319,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12332,13 +12337,13 @@
         <v>83</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12349,10 +12354,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12375,17 +12380,17 @@
         <v>83</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12434,7 +12439,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12458,7 +12463,7 @@
         <v>83</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12469,10 +12474,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12495,13 +12500,13 @@
         <v>83</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12552,7 +12557,7 @@
         <v>83</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12573,10 +12578,10 @@
         <v>83</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>83</v>
@@ -12587,10 +12592,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12613,16 +12618,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12672,7 +12677,7 @@
         <v>83</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12693,10 +12698,10 @@
         <v>83</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>83</v>
@@ -12707,10 +12712,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12733,7 +12738,7 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>162</v>
@@ -12742,7 +12747,7 @@
         <v>162</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12792,7 +12797,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -12813,10 +12818,10 @@
         <v>83</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -12827,10 +12832,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12853,19 +12858,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -12914,7 +12919,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12935,10 +12940,10 @@
         <v>83</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>83</v>
@@ -12949,10 +12954,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12975,13 +12980,13 @@
         <v>83</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13032,7 +13037,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13056,7 +13061,7 @@
         <v>83</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
@@ -13067,10 +13072,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13099,7 +13104,7 @@
         <v>141</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>143</v>
@@ -13152,7 +13157,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13176,7 +13181,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13187,14 +13192,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13216,10 +13221,10 @@
         <v>140</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>143</v>
@@ -13274,7 +13279,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13309,10 +13314,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13338,16 +13343,16 @@
         <v>188</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13372,13 +13377,13 @@
         <v>83</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>83</v>
@@ -13396,7 +13401,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>94</v>
@@ -13414,16 +13419,16 @@
         <v>83</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>83</v>
@@ -13431,10 +13436,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13457,19 +13462,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>83</v>
@@ -13518,7 +13523,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13536,27 +13541,27 @@
         <v>83</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13582,16 +13587,16 @@
         <v>188</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>83</v>
@@ -13616,13 +13621,13 @@
         <v>83</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>83</v>
@@ -13640,7 +13645,7 @@
         <v>83</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13649,7 +13654,7 @@
         <v>94</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>106</v>
@@ -13664,7 +13669,7 @@
         <v>137</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -13675,14 +13680,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13704,16 +13709,16 @@
         <v>188</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -13738,13 +13743,13 @@
         <v>83</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>83</v>
@@ -13762,7 +13767,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13780,27 +13785,27 @@
         <v>83</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13826,16 +13831,16 @@
         <v>84</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>83</v>
@@ -13884,7 +13889,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13905,10 +13910,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
